--- a/input_data_2035_aggregated.xlsx
+++ b/input_data_2035_aggregated.xlsx
@@ -1,16 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29628"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr defaultThemeVersion="124226"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\EEG\EPEC\EPEC_VS_code\SolarGeoRisk_EPEC_extension\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ECF5427E-F02B-4C8C-96CF-F3BD9C124235}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="30930" yWindow="4590" windowWidth="14400" windowHeight="7275" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
     <sheet name="regions" sheetId="1" r:id="rId1"/>
@@ -18,17 +12,17 @@
     <sheet name="c_ship" sheetId="3" r:id="rId3"/>
     <sheet name="settings" sheetId="4" r:id="rId4"/>
   </sheets>
-  <calcPr calcId="124519"/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
     <author/>
   </authors>
   <commentList>
-    <comment ref="B5" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-000001000000}">
+    <comment ref="B5" authorId="0">
       <text>
         <r>
           <rPr>
@@ -42,7 +36,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="C5" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-000002000000}">
+    <comment ref="C5" authorId="0">
       <text>
         <r>
           <rPr>
@@ -61,7 +55,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="37">
   <si>
     <t>r</t>
   </si>
@@ -133,6 +127,12 @@
   </si>
   <si>
     <t>kappa_Q</t>
+  </si>
+  <si>
+    <t>f_hold</t>
+  </si>
+  <si>
+    <t>c_inv</t>
   </si>
   <si>
     <t>exporter</t>
@@ -171,8 +171,8 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <fonts count="3">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -245,21 +245,13 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2007 - 2010">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -297,7 +289,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2007 - 2010">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -331,7 +323,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -366,10 +357,9 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2007 - 2010">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -542,11 +532,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:B6"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -554,7 +544,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:2">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -562,7 +552,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:2">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -570,7 +560,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:2">
       <c r="A4" t="s">
         <v>4</v>
       </c>
@@ -578,7 +568,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:2">
       <c r="A5" t="s">
         <v>5</v>
       </c>
@@ -586,7 +576,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:2">
       <c r="A6" t="s">
         <v>6</v>
       </c>
@@ -600,19 +590,11 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:M6"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <cols>
-    <col min="2" max="2" width="20.36328125" customWidth="1"/>
-    <col min="3" max="3" width="15.453125" customWidth="1"/>
-    <col min="4" max="4" width="18.90625" customWidth="1"/>
-    <col min="5" max="5" width="14.6328125" customWidth="1"/>
-    <col min="6" max="6" width="13" customWidth="1"/>
-    <col min="7" max="7" width="13.81640625" customWidth="1"/>
-  </cols>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:O6"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:15">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -652,8 +634,14 @@
       <c r="M1" s="1" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="N1" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="2" spans="1:15">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -691,10 +679,16 @@
         <v>1.0286</v>
       </c>
       <c r="M2">
-        <v>1E-4</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.35">
+        <v>0.0001</v>
+      </c>
+      <c r="N2">
+        <v>1</v>
+      </c>
+      <c r="O2">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="3" spans="1:15">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -732,10 +726,16 @@
         <v>4.2</v>
       </c>
       <c r="M3">
-        <v>1E-4</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.35">
+        <v>0.0001</v>
+      </c>
+      <c r="N3">
+        <v>1</v>
+      </c>
+      <c r="O3">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15">
       <c r="A4" t="s">
         <v>4</v>
       </c>
@@ -770,13 +770,19 @@
         <v>660</v>
       </c>
       <c r="L4">
-        <v>4.8888999999999996</v>
+        <v>4.8889</v>
       </c>
       <c r="M4">
-        <v>1E-4</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.35">
+        <v>0.0001</v>
+      </c>
+      <c r="N4">
+        <v>1</v>
+      </c>
+      <c r="O4">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15">
       <c r="A5" t="s">
         <v>5</v>
       </c>
@@ -811,13 +817,19 @@
         <v>570</v>
       </c>
       <c r="L5">
-        <v>2.5333000000000001</v>
+        <v>2.5333</v>
       </c>
       <c r="M5">
-        <v>1E-4</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.35">
+        <v>0.0001</v>
+      </c>
+      <c r="N5">
+        <v>1</v>
+      </c>
+      <c r="O5">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15">
       <c r="A6" t="s">
         <v>6</v>
       </c>
@@ -852,10 +864,16 @@
         <v>600</v>
       </c>
       <c r="L6">
-        <v>2.6667000000000001</v>
+        <v>2.6667</v>
       </c>
       <c r="M6">
-        <v>1E-4</v>
+        <v>0.0001</v>
+      </c>
+      <c r="N6">
+        <v>1</v>
+      </c>
+      <c r="O6">
+        <v>48</v>
       </c>
     </row>
   </sheetData>
@@ -865,13 +883,13 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:F6"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:6">
       <c r="A1" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>2</v>
@@ -889,7 +907,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:6">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -909,7 +927,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:6">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -929,7 +947,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:6">
       <c r="A4" t="s">
         <v>4</v>
       </c>
@@ -949,7 +967,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:6">
       <c r="A5" t="s">
         <v>5</v>
       </c>
@@ -969,7 +987,7 @@
         <v>18.5</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:6">
       <c r="A6" t="s">
         <v>6</v>
       </c>
@@ -995,56 +1013,56 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:B6"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
       <c r="A2" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
+      <c r="A3" t="s">
+        <v>30</v>
+      </c>
+      <c r="B3" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
+      <c r="A4" t="s">
+        <v>31</v>
+      </c>
+      <c r="B4" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
+      <c r="A5" t="s">
         <v>32</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A3" t="s">
-        <v>28</v>
-      </c>
-      <c r="B3" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A4" t="s">
-        <v>29</v>
-      </c>
-      <c r="B4" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A5" t="s">
-        <v>30</v>
       </c>
       <c r="B5">
         <v>0.05</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:2">
       <c r="A6" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="B6" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
     </row>
   </sheetData>

--- a/input_data_2035_aggregated.xlsx
+++ b/input_data_2035_aggregated.xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29628"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\EEG\EPEC\EPEC_VS_code\SolarGeoRisk_EPEC_extension\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{77083298-7A54-426C-8887-421054D1F543}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="regions" sheetId="1" r:id="rId1"/>
@@ -12,17 +18,17 @@
     <sheet name="c_ship" sheetId="3" r:id="rId3"/>
     <sheet name="settings" sheetId="4" r:id="rId4"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519"/>
 </workbook>
 </file>
 
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
     <author/>
   </authors>
   <commentList>
-    <comment ref="B5" authorId="0">
+    <comment ref="B5" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-000001000000}">
       <text>
         <r>
           <rPr>
@@ -36,7 +42,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="C5" authorId="0">
+    <comment ref="C5" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-000002000000}">
       <text>
         <r>
           <rPr>
@@ -55,7 +61,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="37">
   <si>
     <t>r</t>
   </si>
@@ -171,8 +177,8 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="3">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -245,13 +251,21 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -289,7 +303,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -323,6 +337,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -357,9 +372,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -532,11 +548,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:B6"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:2">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -544,7 +560,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -552,7 +568,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:2">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -560,7 +576,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="1:2">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>4</v>
       </c>
@@ -568,7 +584,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="5" spans="1:2">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>5</v>
       </c>
@@ -576,7 +592,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="6" spans="1:2">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>6</v>
       </c>
@@ -590,11 +606,15 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:O6"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="2" max="2" width="18.1796875" customWidth="1"/>
+    <col min="3" max="4" width="16" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:15">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -641,7 +661,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="2" spans="1:15">
+    <row r="2" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -679,7 +699,7 @@
         <v>1.0286</v>
       </c>
       <c r="M2">
-        <v>0.0001</v>
+        <v>1E-4</v>
       </c>
       <c r="N2">
         <v>1</v>
@@ -688,7 +708,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="3" spans="1:15">
+    <row r="3" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -726,7 +746,7 @@
         <v>4.2</v>
       </c>
       <c r="M3">
-        <v>0.0001</v>
+        <v>1E-4</v>
       </c>
       <c r="N3">
         <v>1</v>
@@ -735,7 +755,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="4" spans="1:15">
+    <row r="4" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>4</v>
       </c>
@@ -770,10 +790,10 @@
         <v>660</v>
       </c>
       <c r="L4">
-        <v>4.8889</v>
+        <v>4.8888999999999996</v>
       </c>
       <c r="M4">
-        <v>0.0001</v>
+        <v>1E-4</v>
       </c>
       <c r="N4">
         <v>1</v>
@@ -782,7 +802,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="5" spans="1:15">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>5</v>
       </c>
@@ -817,10 +837,10 @@
         <v>570</v>
       </c>
       <c r="L5">
-        <v>2.5333</v>
+        <v>2.5333000000000001</v>
       </c>
       <c r="M5">
-        <v>0.0001</v>
+        <v>1E-4</v>
       </c>
       <c r="N5">
         <v>1</v>
@@ -829,7 +849,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="6" spans="1:15">
+    <row r="6" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>6</v>
       </c>
@@ -864,10 +884,10 @@
         <v>600</v>
       </c>
       <c r="L6">
-        <v>2.6667</v>
+        <v>2.6667000000000001</v>
       </c>
       <c r="M6">
-        <v>0.0001</v>
+        <v>1E-4</v>
       </c>
       <c r="N6">
         <v>1</v>
@@ -883,11 +903,11 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:F6"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:6">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>26</v>
       </c>
@@ -907,7 +927,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:6">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -927,7 +947,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="3" spans="1:6">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -947,7 +967,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="1:6">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>4</v>
       </c>
@@ -967,7 +987,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="5" spans="1:6">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>5</v>
       </c>
@@ -987,7 +1007,7 @@
         <v>18.5</v>
       </c>
     </row>
-    <row r="6" spans="1:6">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>6</v>
       </c>
@@ -1013,11 +1033,11 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:B6"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:2">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>27</v>
       </c>
@@ -1025,7 +1045,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="2" spans="1:2">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>29</v>
       </c>
@@ -1033,7 +1053,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="3" spans="1:2">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>30</v>
       </c>
@@ -1041,7 +1061,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="4" spans="1:2">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>31</v>
       </c>
@@ -1049,7 +1069,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="5" spans="1:2">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>32</v>
       </c>
@@ -1057,7 +1077,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="6" spans="1:2">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>33</v>
       </c>
